--- a/FHIR_Testdatengenerator_Interpolar_Demo.xlsx
+++ b/FHIR_Testdatengenerator_Interpolar_Demo.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="1001">
   <si>
     <t xml:space="preserve">Patient-ID</t>
   </si>
@@ -330,7 +330,7 @@
     <t xml:space="preserve">Nebendiagnose</t>
   </si>
   <si>
-    <t xml:space="preserve">Eine Zeile entspricht einer Diagnose; Zusatzcode bezeichnet dieselbe Diagnose.</t>
+    <t xml:space="preserve">Eine Zeile erzeugt eine Condition; ein Zusatzcoding beschreibt dieselbe Diagnose.</t>
   </si>
   <si>
     <t xml:space="preserve">Vorher bestehende Hypertonie in der Schwangerschaft</t>
@@ -339,16 +339,61 @@
     <t xml:space="preserve">O10</t>
   </si>
   <si>
-    <t xml:space="preserve">Codesystem und Version ausdrücklich auswählen; Codes werden unverändert ausgegeben.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leer bedeutet weglassen. !dar:&lt;Grund&gt; setzt ausdrücklich einen Fehlwert.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beginn, Ende und Dokumentation sind getrennte Zeitangaben.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auswahlwerte stehen im Blatt Codes. Unbekannte SNOMED-Version wird nicht erfunden.</t>
+    <t xml:space="preserve">D/E Code und Codesystem: Condition.code.coding; System und Version ausdrücklich auswählen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F/G Zusatzcode und Zusatzcodesystem: optionales zweites Coding derselben Diagnose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H Dokumentationszeitpunkt → Condition.recordedDate: erstmalige Erfassung dieses Diagnoseeintrags.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Beginn → Condition.onsetDateTime: tatsächlicher oder geschätzter Erkrankungsbeginn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J Ende → Condition.abatementDateTime: Zeitpunkt des Abklingens oder der Remission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ende ist weder Entlassdatum noch Gültigkeitsende der Dokumentation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die drei Zeitfelder werden unabhängig übernommen; keines befüllt automatisch ein anderes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leere Zeitfelder bleiben in Condition leer; auch Fallbeginn und Fallende ersetzen sie nicht.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beispiel: Beginn 03.09., Dokumentation 05.09., Abklingen 10.09. desselben Jahres.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeitformat: TT.MM.JJJJ HH:MM:SS oder FHIR/ISO, z.B. 2026-09-03 bzw. mit Zeitzonenoffset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K Klinischer Status → Condition.clinicalStatus: aktueller Zustand der Erkrankung.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bei ausgefülltem Ende: klinischer Status Inaktiv, Abgeklungen oder Remission wählen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L Verifikationsstatus → Condition.verificationStatus: diagnostische Sicherheit, kein Zeitstempel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C Bezeichner → Condition.code.text: Freitextbeschreibung; M Typ: Diagnoserolle im Fall.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Patient-ID und B Fall-Nr ordnen die Diagnose dem Patienten und Kontakt zu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auswahlwerte stehen im Blatt Codes; Code und Zeit erlauben zusätzlich freie Eingaben.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leer bedeutet weglassen. !dar:&lt;Grund&gt; setzt ausdrücklich einen Fehlwertgrund.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bei Code oder Zusatzcode ist auch für !dar:&lt;Grund&gt; das zugehörige Codesystem anzugeben.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codes werden unverändert ausgegeben; eine fehlende SNOMED-Version wird nicht erfunden.</t>
   </si>
   <si>
     <t xml:space="preserve">Prozedurentext</t>
@@ -501,6 +546,672 @@
     <t xml:space="preserve">Location</t>
   </si>
   <si>
+    <t xml:space="preserve">Aufnahmediagnose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAct *Catalytic Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pt *Point in Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abscess *Abscess  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qn *Quantitative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggl *Agglutination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vor Aufnahme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ätherisches Öl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atemfrequenz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simplifier.net/packages/hl7.fhir.r4.core/4.0.1/files/82753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vorstationaer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geriatrie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einweisungsdiagnose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCnc Catalytic Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stdy *Duration of Study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amnio fld *Amniotic fluid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ord *Ordinal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBA IFA *Cell binding assay immunofluorescent assay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampullen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabe (MedicationAdministration)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzfrequenz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://terminology.hl7.org/CodeSystem/location-physical-type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">divers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vollstationaer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kardiologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fachabteilungsdiagnose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRto Catalytic Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enctr *Duration of Encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anal *Anus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OrdQn *Quantitative or Ordinal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coag *Coagulation Assay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im Verlauf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampullenpaare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angabe (MedicationStatement)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulsoximetrische Sauerstoffsättigung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">si</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A collection of buildings or other locations such as a site or a campus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nachstationaer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nephrologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nachfolgediagnose (mit anschließender Arbeitsunfähigkeit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCnt *Catalytic Content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Episode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asp *Aspirate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nom *Nominal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC *Complement-dependent Cytotoxicity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Am letztzen Tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augen- und Nasensalbe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Körpertemperatur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any Building or structure. This may contain rooms, corridors, wings, etc. It might not have walls, or a roof, but is considered a defined/allocated space.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ambulant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haematologie und internistische Onkologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entlassungsdiagnose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFr *Catalytic Fraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gt 1H *Greater than 1 hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bil fld *Bile fluid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nar *Narrative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comp fix *Complement Fixation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bei Entlassung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augen- und Ohrensalbe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Körpergröße</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Wing within a Building, this often contains levels, rooms and corridors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">teilstationaer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endokrinologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fachabteilungszusatzdiagnose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFr.DF Decimal Catalytic Fraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ge 1 Hr *Greater than or equal 1 hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BldA *Blood arterial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi *“Multi”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyto stain *Cytology Stain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augen- und Ohrentropfen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kopfumfang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Ward is a section of a medical facility that may contain rooms and other types of location.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gastroenterologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Überweisungsdiagnose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRat Catalytic Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lt 1H *Less than 1 hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BldL *Blood bag </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doc *Document</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe *DNA Nucleic Acid Probe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augentropfen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lvl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Level in a multi-level Building/Structure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pneumologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behandlungsdiagnose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelCCnc Relative Catalytic Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedure dur *Duration of Procedure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BldC *Blood capillary </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set *Set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chromo *Chromogenic/Enzymatic Assay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augenbad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">co</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corridor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any corridor within a Building, that may connect rooms.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rheumatologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hauptdiagnose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSub Catalytic Substance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BldCo *Blood – cord </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IA *Immunoassay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augencreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systolischer und Diastolischer Blutdruck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A space that is allocated as a room, it may have walls/roof etc., but does not require these.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paediatrie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EntCat *Entitic Catalytic Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BldMV *Blood- mixed Venous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floc *Flocculation Assay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augengel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systolischer Blutdruck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A space that is allocated for sleeping/laying on. This is not the physical bed/trolley that may be moved about, but the space it may occupy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinderkardiologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EntLen Entitic Length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BldP *Blood – peripheral </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAI *Hemagglutination Inhibition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augensalbe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diastolischer Blutdruck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A means of transportation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neonatologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EntLogNum Logarithmic Entitic Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BldV *Blood venous </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HA *Hemagglutination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blutdruck allgemein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A residential dwelling. Usually used to reference a location that a person/patient may reside.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinderchirurgie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EntMass Entitic Mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bld.dot *Blood filter paper </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IB *Immune Blot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balsam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabinet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A container that can store goods, equipment, medications or other items.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lungen- und Bronchialheilkunde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EntNum *Entitic Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body fld *Body fluid, unsp </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IF *Immune Fluorescence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bandage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A defined path to travel between 2 points that has a known name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allgemeine Chirurgie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EntVol *Entitic Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bone *Bone </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA *Latex Agglutination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beutel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A defined physical boundary of something, such as a flood risk zone, region, postcode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unfallchirurgie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EntSub Entitic Substance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brain *Brain </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LHR *Leukocyte Histamine Release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jdn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jurisdiction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A wide scope that covers a conceptual domain, such as a Nation (Country wide community or Federal Government - e.g. Ministry of Health), Province or State (community or Government), Business (throughout the enterprise), Nation with a business scope of an agency (e.g. CDC, FDA etc.) or a Business segment (UK Pharmacy), not just an physical boundary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neurochirurgie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EntSRto Entitic Substance Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bronchial *Bronchial </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line blot *Line blot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonbons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gefaesschirurgie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mass Mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burn *Burn </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIC *Minimum Inhibitory Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basisplatte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plastische Chirurgie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArMass Mass/Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculus *Calculus (=Stone) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLC *Minimum Lethal Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thoraxchirurgie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCnc *Mass Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cnl *Cannula </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molgen *Molecular Genetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brausetabletten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzchirurgie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCncSq Mass Concentration Squared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTp *Catheter tip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neut *Neutralization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCnt Mass Content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSF *Cerebral spinal fluid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIA *Radioimmunoassay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durchstechflaschen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orthopaedie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDiff Mass Difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cvm *Cervical mucus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPR *Rapid Plasma Reagin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dilution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frauenheilkunde und Geburtshilfe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFr *Mass Fraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cvx *Cervix </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBT *Serum Bacterial Titer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depot-Injektionssuspension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geburtshilfe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFr.DF Mass Decimal Fraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Col *Colostrum </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragees in Kalenderpackung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hals-, Nasen-, Ohrenheilkunde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFrDiff Mass Fraction Difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cnjt *Conjunctiva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAP *Vertical Auto Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosieraerosol</t>
+  </si>
+  <si>
     <t xml:space="preserve">Diagnose: Codesystem und Version</t>
   </si>
   <si>
@@ -513,37 +1224,19 @@
     <t xml:space="preserve">Expliziter Fehlwert (DAR)</t>
   </si>
   <si>
-    <t xml:space="preserve">Aufnahmediagnose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAct *Catalytic Activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt *Point in Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abscess *Abscess  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qn *Quantitative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aggl *Agglutination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vor Aufnahme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ätherisches Öl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atemfrequenz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simplifier.net/packages/hl7.fhir.r4.core/4.0.1/files/82753</t>
+    <t xml:space="preserve">Augenheilkunde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRat Mass Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crn *Cornea </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VC *Visual Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragees</t>
   </si>
   <si>
     <t xml:space="preserve">SNOMED CT (Version nicht angegeben)</t>
@@ -558,43 +1251,19 @@
     <t xml:space="preserve">!dar:unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">vorstationaer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geriatrie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einweisungsdiagnose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCnc Catalytic Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stdy *Duration of Study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amnio fld *Amniotic fluid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ord *Ordinal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBA IFA *Cell binding assay immunofluorescent assay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ampullen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabe (MedicationAdministration)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzfrequenz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://terminology.hl7.org/CodeSystem/location-physical-type</t>
+    <t xml:space="preserve">Neurologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRto Mass Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dentin *Dentin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VDRL *Venereal Disease Research Laboratory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragees magensaftresistent</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2009</t>
@@ -609,52 +1278,16 @@
     <t xml:space="preserve">!dar:asked-unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">divers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vollstationaer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kardiologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fachabteilungsdiagnose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRto Catalytic Ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enctr *Duration of Encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anal *Anus </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OrdQn *Quantitative or Ordinal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coag *Coagulation Assay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Im Verlauf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ampullenpaare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angabe (MedicationStatement)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pulsoximetrische Sauerstoffsättigung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">si</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A collection of buildings or other locations such as a site or a campus.</t>
+    <t xml:space="preserve">Allgemeine Pychiatrie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelMCnc *Relative Mass Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dial fld *Dialysis fluid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosierschaum</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2010</t>
@@ -669,46 +1302,16 @@
     <t xml:space="preserve">!dar:temp-unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">nachstationaer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nephrologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nachfolgediagnose (mit anschließender Arbeitsunfähigkeit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCnt *Catalytic Content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Episode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asp *Aspirate </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nom *Nominal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC *Complement-dependent Cytotoxicity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Am letztzen Tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augen- und Nasensalbe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Körpertemperatur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any Building or structure. This may contain rooms, corridors, wings, etc. It might not have walls, or a roof, but is considered a defined/allocated space.</t>
+    <t xml:space="preserve">Kinder- und Jugendpsychiatrie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelMRat Relative Mass Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dose *Dose med or substance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosierspray</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2011</t>
@@ -723,46 +1326,16 @@
     <t xml:space="preserve">!dar:not-asked</t>
   </si>
   <si>
-    <t xml:space="preserve">ambulant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haematologie und internistische Onkologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entlassungsdiagnose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFr *Catalytic Fraction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gt 1H *Greater than 1 hour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bil fld *Bile fluid </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nar *Narrative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comp fix *Complement Fixation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bei Entlassung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augen- und Ohrensalbe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Körpergröße</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Wing within a Building, this often contains levels, rooms and corridors.</t>
+    <t xml:space="preserve">Psychosomatik/Psychotherapie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThrMCnc *Threshold Mass Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drain *Drain </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einzeldosis-Pipetten</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2012</t>
@@ -777,43 +1350,16 @@
     <t xml:space="preserve">!dar:asked-declined</t>
   </si>
   <si>
-    <t xml:space="preserve">teilstationaer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endokrinologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fachabteilungszusatzdiagnose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFr.DF Decimal Catalytic Fraction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ge 1 Hr *Greater than or equal 1 hour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BldA *Blood arterial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi *“Multi”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyto stain *Cytology Stain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augen- und Ohrentropfen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kopfumfang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Ward is a section of a medical facility that may contain rooms and other types of location.</t>
+    <t xml:space="preserve">Nuklearmedizin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCncDiff Difference in Mass Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duod fld *Duodenal fluid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einreibung</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2013</t>
@@ -828,37 +1374,16 @@
     <t xml:space="preserve">!dar:masked</t>
   </si>
   <si>
-    <t xml:space="preserve">Gastroenterologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Überweisungsdiagnose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRat Catalytic Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lt 1H *Less than 1 hour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BldL *Blood bag </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doc *Document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probe *DNA Nucleic Acid Probe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augentropfen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lvl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Level in a multi-level Building/Structure.</t>
+    <t xml:space="preserve">Strahlenheilkunde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCPctDiff Percent Difference in Mass Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ear *Ear </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elektroden</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2014</t>
@@ -867,40 +1392,16 @@
     <t xml:space="preserve">!dar:not-applicable</t>
   </si>
   <si>
-    <t xml:space="preserve">Pneumologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Behandlungsdiagnose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RelCCnc Relative Catalytic Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedure dur *Duration of Procedure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BldC *Blood capillary </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set *Set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chromo *Chromogenic/Enzymatic Assay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augenbad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corridor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any corridor within a Building, that may connect rooms.</t>
+    <t xml:space="preserve">Dermatologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelSCnc *Relative Substance Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endomet *Endometrium </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elixier</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2015</t>
@@ -909,34 +1410,16 @@
     <t xml:space="preserve">!dar:unsupported</t>
   </si>
   <si>
-    <t xml:space="preserve">Rheumatologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hauptdiagnose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSub Catalytic Substance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BldCo *Blood – cord </t>
-  </si>
-  <si>
-    <t xml:space="preserve">IA *Immunoassay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augencreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systolischer und Diastolischer Blutdruck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A space that is allocated as a room, it may have walls/roof etc., but does not require these.</t>
+    <t xml:space="preserve">Zahn- und Kieferheilkunde, Mund- und Kieferchirurgie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub *Substance Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environmental Specimen *Environmental Specimen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emulsion</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2016</t>
@@ -945,31 +1428,16 @@
     <t xml:space="preserve">!dar:as-text</t>
   </si>
   <si>
-    <t xml:space="preserve">Paediatrie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EntCat *Entitic Catalytic Activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BldMV *Blood- mixed Venous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floc *Flocculation Assay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augengel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systolischer Blutdruck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A space that is allocated for sleeping/laying on. This is not the physical bed/trolley that may be moved about, but the space it may occupy.</t>
+    <t xml:space="preserve">Intensivmedizin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCnc *Substance Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBC *Erythrocytes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Essenz</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2017</t>
@@ -978,31 +1446,16 @@
     <t xml:space="preserve">!dar:error</t>
   </si>
   <si>
-    <t xml:space="preserve">Kinderkardiologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EntLen Entitic Length</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BldP *Blood – peripheral </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAI *Hemagglutination Inhibition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augensalbe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diastolischer Blutdruck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A means of transportation.</t>
+    <t xml:space="preserve">Orthopaedie und Unfallchirurgie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCncSq Substance Concentration Squared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eye *Eye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erwachsenen-Suppositorien</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2018</t>
@@ -1011,31 +1464,16 @@
     <t xml:space="preserve">!dar:not-a-number</t>
   </si>
   <si>
-    <t xml:space="preserve">Neonatologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EntLogNum Logarithmic Entitic Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BldV *Blood venous </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HA *Hemagglutination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blutdruck allgemein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A residential dwelling. Usually used to reference a location that a person/patient may reside.</t>
+    <t xml:space="preserve">Frauenheilkunde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRto *Substance Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exhl gas *Exhaled gas (breath)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extrakt</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2019</t>
@@ -1044,28 +1482,16 @@
     <t xml:space="preserve">!dar:negative-infinity</t>
   </si>
   <si>
-    <t xml:space="preserve">Kinderchirurgie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EntMass Entitic Mass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bld.dot *Blood filter paper </t>
-  </si>
-  <si>
-    <t xml:space="preserve">IB *Immune Blot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balsam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabinet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A container that can store goods, equipment, medications or other items.</t>
+    <t xml:space="preserve">Sonstige Fachabteilung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCnt *Substance Content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fibroblasts *Fibroblasts </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filterbeutel</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2020</t>
@@ -1074,28 +1500,13 @@
     <t xml:space="preserve">!dar:positive-infinity</t>
   </si>
   <si>
-    <t xml:space="preserve">Lungen- und Bronchialheilkunde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EntNum *Entitic Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Body fld *Body fluid, unsp </t>
-  </si>
-  <si>
-    <t xml:space="preserve">IF *Immune Fluorescence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bandage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Road</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A defined path to travel between 2 points that has a known name.</t>
+    <t xml:space="preserve">SFr *Substance Fraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fistula *Fistula </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franzbranntwein</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2021</t>
@@ -1104,28 +1515,13 @@
     <t xml:space="preserve">!dar:not-performed</t>
   </si>
   <si>
-    <t xml:space="preserve">Allgemeine Chirurgie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EntVol *Entitic Volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bone *Bone </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA *Latex Agglutination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beutel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A defined physical boundary of something, such as a flood risk zone, region, postcode</t>
+    <t xml:space="preserve">SFr.DF Decimal Substance Fraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food *Food sample </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filmdragees</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2022</t>
@@ -1134,400 +1530,49 @@
     <t xml:space="preserve">!dar:not-permitted</t>
   </si>
   <si>
-    <t xml:space="preserve">Unfallchirurgie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EntSub Entitic Substance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brain *Brain </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LHR *Leukocyte Histamine Release</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jdn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jurisdiction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A wide scope that covers a conceptual domain, such as a Nation (Country wide community or Federal Government - e.g. Ministry of Health), Province or State (community or Government), Business (throughout the enterprise), Nation with a business scope of an agency (e.g. CDC, FDA etc.) or a Business segment (UK Pharmacy), not just an physical boundary</t>
+    <t xml:space="preserve">SRat *Substance Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gas *Gas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fertigspritzen</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2023</t>
   </si>
   <si>
-    <t xml:space="preserve">Neurochirurgie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EntSRto Entitic Substance Ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bronchial *Bronchial </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Line blot *Line blot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bonbons</t>
+    <t xml:space="preserve">RelSRat Relative Substance Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gast fld *Gastric Fluid/Contents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fettsalbe</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2024</t>
   </si>
   <si>
-    <t xml:space="preserve">Gefaesschirurgie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mass Mass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burn *Burn </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIC *Minimum Inhibitory Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basisplatte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plastische Chirurgie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ArMass Mass/Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calculus *Calculus (=Stone) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLC *Minimum Lethal Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brei</t>
+    <t xml:space="preserve">ThrSCnc Threshold Substance Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genital *Genital </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flasche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCncDiff Difference in Substance Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genital fld *Genital fluid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flüssigkeit zum Einnehmen</t>
   </si>
   <si>
     <t xml:space="preserve">ICD-10-GM 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thoraxchirurgie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCnc *Mass Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cnl *Cannula </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molgen *Molecular Genetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brausetabletten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzchirurgie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCncSq Mass Concentration Squared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTp *Catheter tip </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neut *Neutralization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCnt Mass Content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSF *Cerebral spinal fluid </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RIA *Radioimmunoassay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durchstechflaschen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orthopaedie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDiff Mass Difference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cvm *Cervical mucus </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPR *Rapid Plasma Reagin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dilution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frauenheilkunde und Geburtshilfe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFr *Mass Fraction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cvx *Cervix </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SBT *Serum Bacterial Titer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depot-Injektionssuspension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geburtshilfe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFr.DF Mass Decimal Fraction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Col *Colostrum </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragees in Kalenderpackung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hals-, Nasen-, Ohrenheilkunde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFrDiff Mass Fraction Difference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cnjt *Conjunctiva </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAP *Vertical Auto Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosieraerosol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augenheilkunde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRat Mass Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crn *Cornea </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VC *Visual Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neurologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRto Mass Ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dentin *Dentin </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VDRL *Venereal Disease Research Laboratory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragees magensaftresistent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allgemeine Pychiatrie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RelMCnc *Relative Mass Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dial fld *Dialysis fluid </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosierschaum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kinder- und Jugendpsychiatrie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RelMRat Relative Mass Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dose *Dose med or substance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosierspray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Psychosomatik/Psychotherapie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThrMCnc *Threshold Mass Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drain *Drain </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einzeldosis-Pipetten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuklearmedizin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCncDiff Difference in Mass Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duod fld *Duodenal fluid </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einreibung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strahlenheilkunde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCPctDiff Percent Difference in Mass Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ear *Ear </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elektroden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dermatologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RelSCnc *Relative Substance Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endomet *Endometrium </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elixier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zahn- und Kieferheilkunde, Mund- und Kieferchirurgie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sub *Substance Amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environmental Specimen *Environmental Specimen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emulsion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intensivmedizin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCnc *Substance Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBC *Erythrocytes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Essenz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orthopaedie und Unfallchirurgie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCncSq Substance Concentration Squared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eye *Eye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erwachsenen-Suppositorien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frauenheilkunde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRto *Substance Ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exhl gas *Exhaled gas (breath)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extrakt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sonstige Fachabteilung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCnt *Substance Content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fibroblasts *Fibroblasts </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filterbeutel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SFr *Substance Fraction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fistula *Fistula </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Franzbranntwein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SFr.DF Decimal Substance Fraction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Food *Food sample </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filmdragees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRat *Substance Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gas *Gas </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fertigspritzen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RelSRat Relative Substance Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gast fld *Gastric Fluid/Contents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fettsalbe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThrSCnc Threshold Substance Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genital *Genital </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flasche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCncDiff Difference in Substance Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genital fld *Genital fluid </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flüssigkeit zum Einnehmen</t>
   </si>
   <si>
     <t xml:space="preserve">LsCnc Log Substance Concentration</t>
@@ -6844,42 +6889,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="33" t="s">
-        <v>893</v>
+        <v>908</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="33" t="s">
-        <v>894</v>
+        <v>909</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>895</v>
+        <v>910</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
-        <v>896</v>
+        <v>911</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>897</v>
+        <v>912</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>898</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>893</v>
+        <v>908</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6887,92 +6932,92 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>902</v>
+        <v>917</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>903</v>
+        <v>918</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>904</v>
+        <v>919</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>906</v>
+        <v>921</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>907</v>
+        <v>922</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>908</v>
+        <v>923</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>909</v>
+        <v>924</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="33" t="s">
-        <v>910</v>
+        <v>925</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="33" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>912</v>
+        <v>927</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="33" t="s">
-        <v>913</v>
+        <v>928</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="33" t="s">
-        <v>914</v>
+        <v>929</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="33" t="s">
-        <v>915</v>
+        <v>930</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="33" t="s">
-        <v>916</v>
+        <v>931</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6983,27 +7028,27 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="33" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="33" t="s">
-        <v>917</v>
+        <v>932</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="33" t="s">
-        <v>918</v>
+        <v>933</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="33" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="34" t="s">
-        <v>919</v>
+        <v>934</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7011,27 +7056,27 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="33" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="33" t="s">
-        <v>920</v>
+        <v>935</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="33" t="s">
-        <v>918</v>
+        <v>933</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="33" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="33" t="s">
-        <v>921</v>
+        <v>936</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7039,502 +7084,502 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="33" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="33" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="33" t="s">
-        <v>923</v>
+        <v>938</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="33" t="s">
-        <v>924</v>
+        <v>939</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="33" t="s">
-        <v>925</v>
+        <v>940</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="35" t="s">
-        <v>926</v>
+        <v>941</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="32" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="32" t="s">
-        <v>927</v>
+        <v>942</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="32" t="s">
-        <v>928</v>
+        <v>943</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="32" t="s">
-        <v>929</v>
+        <v>944</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="32" t="s">
-        <v>930</v>
+        <v>945</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="35" t="s">
-        <v>931</v>
+        <v>946</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="32" t="s">
-        <v>932</v>
+        <v>947</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="32" t="s">
-        <v>933</v>
+        <v>948</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="32" t="s">
-        <v>934</v>
+        <v>949</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="35" t="s">
-        <v>935</v>
+        <v>950</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="32" t="s">
-        <v>936</v>
+        <v>951</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="32" t="s">
-        <v>937</v>
+        <v>952</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="32" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="32" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="32" t="s">
-        <v>940</v>
+        <v>955</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="32" t="s">
-        <v>941</v>
+        <v>956</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="32" t="s">
-        <v>942</v>
+        <v>957</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="32" t="s">
-        <v>943</v>
+        <v>958</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="32" t="s">
-        <v>944</v>
+        <v>959</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="32" t="s">
-        <v>945</v>
+        <v>960</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="35" t="s">
-        <v>946</v>
+        <v>961</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="32" t="s">
-        <v>947</v>
+        <v>962</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="32" t="s">
-        <v>948</v>
+        <v>963</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="32" t="s">
-        <v>949</v>
+        <v>964</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="32" t="s">
-        <v>950</v>
+        <v>965</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="32" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="32" t="s">
-        <v>951</v>
+        <v>966</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="32" t="s">
-        <v>952</v>
+        <v>967</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="32" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="32" t="s">
-        <v>954</v>
+        <v>969</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="32" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="32" t="s">
-        <v>944</v>
+        <v>959</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="32" t="s">
-        <v>956</v>
+        <v>971</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="35" t="s">
-        <v>957</v>
+        <v>972</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="32" t="s">
-        <v>936</v>
+        <v>951</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="32" t="s">
-        <v>958</v>
+        <v>973</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="32" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="32" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="32" t="s">
-        <v>959</v>
+        <v>974</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="32" t="s">
-        <v>941</v>
+        <v>956</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="32" t="s">
-        <v>942</v>
+        <v>957</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="32" t="s">
-        <v>960</v>
+        <v>975</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="32" t="s">
-        <v>944</v>
+        <v>959</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="32" t="s">
-        <v>945</v>
+        <v>960</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="35" t="s">
-        <v>961</v>
+        <v>976</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="32" t="s">
-        <v>947</v>
+        <v>962</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="32" t="s">
-        <v>948</v>
+        <v>963</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="32" t="s">
-        <v>949</v>
+        <v>964</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="32" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="32" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="32" t="s">
-        <v>963</v>
+        <v>978</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="32" t="s">
-        <v>952</v>
+        <v>967</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="32" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="32" t="s">
-        <v>954</v>
+        <v>969</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="32" t="s">
-        <v>964</v>
+        <v>979</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="32" t="s">
-        <v>944</v>
+        <v>959</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="32" t="s">
-        <v>956</v>
+        <v>971</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="35" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="32" t="s">
-        <v>966</v>
+        <v>981</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="32" t="s">
-        <v>967</v>
+        <v>982</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="32" t="s">
-        <v>968</v>
+        <v>983</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="32" t="s">
-        <v>969</v>
+        <v>984</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="32" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="32" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="32" t="s">
-        <v>972</v>
+        <v>987</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="32" t="s">
-        <v>973</v>
+        <v>988</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="32" t="s">
-        <v>974</v>
+        <v>989</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="35" t="s">
-        <v>975</v>
+        <v>990</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="32" t="s">
-        <v>976</v>
+        <v>991</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="32" t="s">
-        <v>977</v>
+        <v>992</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="32" t="s">
-        <v>978</v>
+        <v>993</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="32" t="s">
-        <v>979</v>
+        <v>994</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="32" t="s">
-        <v>980</v>
+        <v>995</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="32" t="s">
-        <v>981</v>
+        <v>996</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="32" t="s">
-        <v>982</v>
+        <v>997</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="32" t="s">
-        <v>974</v>
+        <v>989</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="32" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="35" t="s">
-        <v>983</v>
+        <v>998</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="32" t="s">
-        <v>984</v>
+        <v>999</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="32" t="s">
-        <v>985</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -7817,12 +7862,12 @@
       <formula1>Codes!$B$4:$B$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E22" type="list">
-      <formula1>Codes!$B$4:$B$9</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F22" type="list">
+      <formula1>Codes!$C$4:$C$42</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F22" type="list">
-      <formula1>Codes!$C$4:$C$42</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E1007" type="list">
+      <formula1>Codes!$B$4:$B$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -10282,6 +10327,9 @@
       <c r="G7" s="17"/>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
+      <c r="N7" s="4" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="8" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D8" s="17"/>
@@ -10290,6 +10338,9 @@
       <c r="G8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
+      <c r="N8" s="4" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="9" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D9" s="17"/>
@@ -10298,6 +10349,9 @@
       <c r="G9" s="17"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
+      <c r="N9" s="4" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="10" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D10" s="17"/>
@@ -10306,6 +10360,9 @@
       <c r="G10" s="17"/>
       <c r="K10" s="17"/>
       <c r="L10" s="17"/>
+      <c r="N10" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="11" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D11" s="17"/>
@@ -10314,6 +10371,9 @@
       <c r="G11" s="17"/>
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
+      <c r="N11" s="4" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="12" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D12" s="17"/>
@@ -10322,6 +10382,9 @@
       <c r="G12" s="17"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
+      <c r="N12" s="4" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="13" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D13" s="17"/>
@@ -10330,6 +10393,9 @@
       <c r="G13" s="17"/>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
+      <c r="N13" s="4" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="14" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D14" s="17"/>
@@ -10338,6 +10404,9 @@
       <c r="G14" s="17"/>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
+      <c r="N14" s="4" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="15" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D15" s="17"/>
@@ -10346,6 +10415,9 @@
       <c r="G15" s="17"/>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
+      <c r="N15" s="4" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="16" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D16" s="17"/>
@@ -10354,6 +10426,9 @@
       <c r="G16" s="17"/>
       <c r="K16" s="17"/>
       <c r="L16" s="17"/>
+      <c r="N16" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="17" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D17" s="17"/>
@@ -10362,6 +10437,9 @@
       <c r="G17" s="17"/>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
+      <c r="N17" s="4" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="18" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D18" s="17"/>
@@ -10370,6 +10448,9 @@
       <c r="G18" s="17"/>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
+      <c r="N18" s="4" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="19" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D19" s="17"/>
@@ -10378,6 +10459,9 @@
       <c r="G19" s="17"/>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
+      <c r="N19" s="4" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="20" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D20" s="17"/>
@@ -10386,6 +10470,9 @@
       <c r="G20" s="17"/>
       <c r="K20" s="17"/>
       <c r="L20" s="17"/>
+      <c r="N20" s="4" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="21" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D21" s="17"/>
@@ -10394,6 +10481,9 @@
       <c r="G21" s="17"/>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
+      <c r="N21" s="4" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="22" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D22" s="17"/>
@@ -18282,19 +18372,19 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E1006 G2:G1006" type="list">
-      <formula1>Codes!$W$4:$W$22</formula1>
+      <formula1>Codes!$W$30:$W$48</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K2:K1006" type="list">
-      <formula1>Codes!$X$4:$X$24</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K1006" type="list">
+      <formula1>Codes!$X$30:$X$50</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="L2:L1006" type="list">
-      <formula1>Codes!$Y$4:$Y$24</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L1006" type="list">
+      <formula1>Codes!$Y$30:$Y$50</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D2:D1006 F2:F1006 H2:J1006" type="list">
-      <formula1>Codes!$Z$4:$Z$18</formula1>
+      <formula1>Codes!$Z$30:$Z$44</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -18336,10 +18426,10 @@
         <v>34</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="E1" s="20" t="s">
         <v>74</v>
@@ -18436,46 +18526,46 @@
         <v>34</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="H1" s="26" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>60</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>13</v>
@@ -18492,22 +18582,22 @@
         <v>46115.375</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="L2" s="7" t="n">
         <v>46115.375</v>
@@ -18519,13 +18609,13 @@
         <v>1</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="P2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18539,22 +18629,22 @@
         <v>46115.375</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>46115.375</v>
@@ -18566,13 +18656,13 @@
         <v>1</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="P3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18586,22 +18676,22 @@
         <v>46115.375</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="L4" s="7" t="n">
         <v>46115.375</v>
@@ -18613,13 +18703,13 @@
         <v>1</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="P4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18633,22 +18723,22 @@
         <v>46115.375</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="L5" s="7" t="n">
         <v>46115.375</v>
@@ -18658,13 +18748,13 @@
         <v>1</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="P5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -23637,13 +23727,13 @@
         <v>57</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>60</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>13</v>
@@ -23657,16 +23747,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="E2" s="11" t="n">
         <v>82</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>46115.3541666667</v>
@@ -23681,16 +23771,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="E3" s="11" t="n">
         <v>176</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>46115.3576388889</v>
@@ -23705,16 +23795,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>74</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>46115.3541666667</v>
@@ -23729,16 +23819,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>180</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>46115.3576388889</v>
@@ -23753,16 +23843,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>68</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>46115.3541666667</v>
@@ -23777,16 +23867,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>168</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>46115.3576388889</v>
@@ -23868,10 +23958,10 @@
         <v>34</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>13</v>
@@ -23933,10 +24023,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D2" s="29" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="F2" s="30"/>
       <c r="G2" s="30"/>
@@ -23955,50 +24045,42 @@
       </c>
       <c r="D3" s="29"/>
       <c r="E3" s="4" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="W3" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="X3" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y3" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z3" s="17" t="s">
-        <v>143</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
@@ -24011,915 +24093,763 @@
         <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="K4" s="31" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>39</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="W4" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="X4" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y4" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z4" s="16" t="s">
-        <v>158</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="W4" s="16"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>40</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="W5" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="X5" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y5" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="Z5" s="16" t="s">
-        <v>175</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>41</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="W6" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="X6" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="Y6" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="Z6" s="16" t="s">
-        <v>195</v>
-      </c>
+      <c r="W6" s="16"/>
+      <c r="X6" s="16"/>
+      <c r="Y6" s="16"/>
+      <c r="Z6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="K7" s="31" t="s">
+      <c r="N7" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="S7" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="T7" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="U7" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="U7" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="W7" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="X7" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y7" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="Z7" s="16" t="s">
-        <v>213</v>
-      </c>
+      <c r="W7" s="16"/>
+      <c r="X7" s="16"/>
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="K8" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="S8" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="T8" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="U8" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="K8" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="W8" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="X8" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="Y8" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="Z8" s="16" t="s">
-        <v>231</v>
-      </c>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="S9" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="T9" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="U9" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="W9" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="X9" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="Y9" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="Z9" s="16" t="s">
-        <v>248</v>
-      </c>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="K10" s="31" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="W10" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="X10" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y10" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="Z10" s="16" t="s">
-        <v>261</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C11" s="1" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="K11" s="31" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="W11" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="X11" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y11" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z11" s="16" t="s">
-        <v>275</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="K12" s="31" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="W12" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="X12" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y12" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="Z12" s="16" t="s">
-        <v>287</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="K13" s="31" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="W13" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="X13" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="Y13" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="Z13" s="16" t="s">
-        <v>298</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="W13" s="16"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="16"/>
+      <c r="Z13" s="16"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="K14" s="31" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="W14" s="16" t="s">
-        <v>308</v>
-      </c>
-      <c r="X14" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="Y14" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="Z14" s="16" t="s">
-        <v>309</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="W14" s="16"/>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="16"/>
+      <c r="Z14" s="16"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="W15" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="X15" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="Y15" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="Z15" s="16" t="s">
-        <v>320</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="16"/>
+      <c r="Z15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C16" s="1" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="K16" s="31" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="W16" s="16" t="s">
-        <v>329</v>
-      </c>
-      <c r="X16" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="Y16" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z16" s="16" t="s">
-        <v>330</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="W16" s="16"/>
+      <c r="X16" s="16"/>
+      <c r="Y16" s="16"/>
+      <c r="Z16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
-        <v>331</v>
+        <v>304</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>332</v>
+        <v>305</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>333</v>
+        <v>306</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>334</v>
+        <v>307</v>
       </c>
       <c r="K17" s="31" t="s">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>336</v>
+        <v>309</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="W17" s="16" t="s">
-        <v>339</v>
-      </c>
-      <c r="X17" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="Y17" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="Z17" s="16" t="s">
-        <v>340</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="W17" s="16"/>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="16"/>
+      <c r="Z17" s="16"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="K18" s="31" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>347</v>
+        <v>318</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="W18" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="X18" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="Y18" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z18" s="16" t="s">
-        <v>350</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="W18" s="16"/>
+      <c r="X18" s="16"/>
+      <c r="Y18" s="16"/>
+      <c r="Z18" s="16"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>354</v>
+        <v>323</v>
       </c>
       <c r="K19" s="31" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="W19" s="16" t="s">
-        <v>359</v>
-      </c>
-      <c r="X19" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="Y19" s="16" t="s">
-        <v>298</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16"/>
+      <c r="Y19" s="16"/>
       <c r="Z19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>363</v>
+        <v>331</v>
       </c>
       <c r="K20" s="31" t="s">
-        <v>364</v>
-      </c>
-      <c r="W20" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="X20" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="Y20" s="16" t="s">
-        <v>309</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="W20" s="16"/>
+      <c r="X20" s="16"/>
+      <c r="Y20" s="16"/>
       <c r="Z20" s="16"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>366</v>
+        <v>333</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>367</v>
+        <v>334</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>368</v>
+        <v>335</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>369</v>
+        <v>336</v>
       </c>
       <c r="K21" s="31" t="s">
-        <v>370</v>
-      </c>
-      <c r="W21" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="X21" s="16" t="s">
-        <v>320</v>
-      </c>
-      <c r="Y21" s="16" t="s">
-        <v>320</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="W21" s="16"/>
+      <c r="X21" s="16"/>
+      <c r="Y21" s="16"/>
       <c r="Z21" s="16"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C22" s="1" t="s">
-        <v>371</v>
+        <v>338</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>372</v>
+        <v>339</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>373</v>
+        <v>340</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>374</v>
+        <v>341</v>
       </c>
       <c r="K22" s="31" t="s">
-        <v>375</v>
-      </c>
-      <c r="W22" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="X22" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="Y22" s="16" t="s">
-        <v>330</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="W22" s="16"/>
+      <c r="X22" s="16"/>
+      <c r="Y22" s="16"/>
       <c r="Z22" s="16"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>380</v>
+        <v>346</v>
       </c>
       <c r="K23" s="31" t="s">
-        <v>381</v>
+        <v>347</v>
       </c>
       <c r="W23" s="16"/>
-      <c r="X23" s="16" t="s">
-        <v>340</v>
-      </c>
-      <c r="Y23" s="16" t="s">
-        <v>340</v>
-      </c>
+      <c r="X23" s="16"/>
+      <c r="Y23" s="16"/>
       <c r="Z23" s="16"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>382</v>
+        <v>348</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="K24" s="31" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="W24" s="16"/>
-      <c r="X24" s="16" t="s">
-        <v>350</v>
-      </c>
-      <c r="Y24" s="16" t="s">
-        <v>350</v>
-      </c>
+      <c r="X24" s="16"/>
+      <c r="Y24" s="16"/>
       <c r="Z24" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>388</v>
+        <v>354</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="K25" s="31" t="s">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="W25" s="16"/>
       <c r="X25" s="16"/>
@@ -24928,19 +24858,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>392</v>
+        <v>358</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>394</v>
+        <v>360</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="K26" s="31" t="s">
-        <v>396</v>
+        <v>362</v>
       </c>
       <c r="W26" s="16"/>
       <c r="X26" s="16"/>
@@ -24949,19 +24879,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="K27" s="31" t="s">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="W27" s="16"/>
       <c r="X27" s="16"/>
@@ -24970,19 +24900,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>404</v>
+        <v>370</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="K28" s="31" t="s">
-        <v>405</v>
+        <v>371</v>
       </c>
       <c r="W28" s="16"/>
       <c r="X28" s="16"/>
@@ -24991,192 +24921,272 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
-        <v>406</v>
+        <v>372</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>409</v>
+        <v>375</v>
       </c>
       <c r="K29" s="31" t="s">
-        <v>410</v>
-      </c>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="Y29" s="16"/>
-      <c r="Z29" s="16"/>
+        <v>376</v>
+      </c>
+      <c r="W29" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="X29" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="Y29" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="Z29" s="17" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>413</v>
+        <v>383</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="K30" s="31" t="s">
-        <v>415</v>
-      </c>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
-      <c r="Z30" s="16"/>
+        <v>385</v>
+      </c>
+      <c r="W30" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="X30" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="Y30" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="Z30" s="16" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C31" s="1" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="K31" s="31" t="s">
-        <v>420</v>
-      </c>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
-      <c r="Y31" s="16"/>
-      <c r="Z31" s="16"/>
+        <v>394</v>
+      </c>
+      <c r="W31" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="X31" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="Y31" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="Z31" s="16" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C32" s="1" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="K32" s="31" t="s">
-        <v>424</v>
-      </c>
-      <c r="W32" s="16"/>
-      <c r="X32" s="16"/>
-      <c r="Y32" s="16"/>
-      <c r="Z32" s="16"/>
+        <v>402</v>
+      </c>
+      <c r="W32" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="X32" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="Y32" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="Z32" s="16" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C33" s="1" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="K33" s="31" t="s">
-        <v>428</v>
-      </c>
-      <c r="W33" s="16"/>
-      <c r="X33" s="16"/>
-      <c r="Y33" s="16"/>
-      <c r="Z33" s="16"/>
+        <v>410</v>
+      </c>
+      <c r="W33" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="X33" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="Y33" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="Z33" s="16" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C34" s="1" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="K34" s="31" t="s">
-        <v>432</v>
-      </c>
-      <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
-      <c r="Y34" s="16"/>
-      <c r="Z34" s="16"/>
+        <v>418</v>
+      </c>
+      <c r="W34" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="X34" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="Y34" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="Z34" s="16" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C35" s="1" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="K35" s="31" t="s">
-        <v>436</v>
-      </c>
-      <c r="W35" s="16"/>
-      <c r="X35" s="16"/>
-      <c r="Y35" s="16"/>
-      <c r="Z35" s="16"/>
+        <v>426</v>
+      </c>
+      <c r="W35" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="X35" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="Y35" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="Z35" s="16" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C36" s="1" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="K36" s="31" t="s">
-        <v>440</v>
-      </c>
-      <c r="W36" s="16"/>
-      <c r="X36" s="16"/>
-      <c r="Y36" s="16"/>
-      <c r="Z36" s="16"/>
+        <v>434</v>
+      </c>
+      <c r="W36" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="X36" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="Y36" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="Z36" s="16" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C37" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="K37" s="31" t="s">
+        <v>440</v>
+      </c>
+      <c r="W37" s="16" t="s">
         <v>441</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="X37" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="Y37" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z37" s="16" t="s">
         <v>442</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="K37" s="31" t="s">
-        <v>444</v>
-      </c>
-      <c r="W37" s="16"/>
-      <c r="X37" s="16"/>
-      <c r="Y37" s="16"/>
-      <c r="Z37" s="16"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C38" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="K38" s="31" t="s">
         <v>446</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="W38" s="16" t="s">
         <v>447</v>
       </c>
-      <c r="K38" s="31" t="s">
+      <c r="X38" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="Y38" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="Z38" s="16" t="s">
         <v>448</v>
       </c>
-      <c r="W38" s="16"/>
-      <c r="X38" s="16"/>
-      <c r="Y38" s="16"/>
-      <c r="Z38" s="16"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C39" s="1" t="s">
@@ -25191,1765 +25201,1885 @@
       <c r="K39" s="31" t="s">
         <v>452</v>
       </c>
-      <c r="W39" s="16"/>
-      <c r="X39" s="16"/>
-      <c r="Y39" s="16"/>
-      <c r="Z39" s="16"/>
+      <c r="W39" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="X39" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="Y39" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="Z39" s="16" t="s">
+        <v>454</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C40" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K40" s="31" t="s">
-        <v>456</v>
-      </c>
-      <c r="W40" s="16"/>
-      <c r="X40" s="16"/>
-      <c r="Y40" s="16"/>
-      <c r="Z40" s="16"/>
+        <v>458</v>
+      </c>
+      <c r="W40" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="X40" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="Y40" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z40" s="16" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C41" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="K41" s="31" t="s">
-        <v>460</v>
+        <v>464</v>
+      </c>
+      <c r="W41" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="X41" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="Y41" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="Z41" s="16" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C42" s="1" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="K42" s="31" t="s">
-        <v>464</v>
+        <v>470</v>
+      </c>
+      <c r="W42" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="X42" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="Y42" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="Z42" s="16" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E43" s="1" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="K43" s="31" t="s">
-        <v>467</v>
+        <v>475</v>
+      </c>
+      <c r="W43" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="X43" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="Y43" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="Z43" s="16" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E44" s="1" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="K44" s="31" t="s">
-        <v>470</v>
+        <v>480</v>
+      </c>
+      <c r="W44" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="X44" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="Y44" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="Z44" s="16" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E45" s="1" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="K45" s="31" t="s">
-        <v>473</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="W45" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="X45" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="Y45" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="Z45" s="16"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E46" s="1" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="K46" s="31" t="s">
-        <v>476</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="W46" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="X46" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="Y46" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="Z46" s="16"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E47" s="1" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="K47" s="31" t="s">
-        <v>479</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="W47" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="X47" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="Y47" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="Z47" s="16"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E48" s="1" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="K48" s="31" t="s">
-        <v>482</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="W48" s="16" t="s">
+        <v>497</v>
+      </c>
+      <c r="X48" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="Y48" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="Z48" s="16"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E49" s="1" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="K49" s="31" t="s">
-        <v>485</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="W49" s="16"/>
+      <c r="X49" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="Y49" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="Z49" s="16"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E50" s="1" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="K50" s="31" t="s">
-        <v>488</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="W50" s="16"/>
+      <c r="X50" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="Y50" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="Z50" s="16"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E51" s="1" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="K51" s="31" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E52" s="1" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="K52" s="31" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E53" s="1" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="K53" s="31" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E54" s="1" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="K54" s="31" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E55" s="1" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="K55" s="31" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E56" s="1" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="K56" s="31" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E57" s="1" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="K57" s="31" t="s">
-        <v>509</v>
+        <v>524</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E58" s="1" t="s">
-        <v>510</v>
+        <v>525</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>511</v>
+        <v>526</v>
       </c>
       <c r="K58" s="31" t="s">
-        <v>512</v>
+        <v>527</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E59" s="1" t="s">
-        <v>513</v>
+        <v>528</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>514</v>
+        <v>529</v>
       </c>
       <c r="K59" s="31" t="s">
-        <v>515</v>
+        <v>530</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E60" s="1" t="s">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="K60" s="31" t="s">
-        <v>518</v>
+        <v>533</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E61" s="1" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="K61" s="31" t="s">
-        <v>521</v>
+        <v>536</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E62" s="1" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="K62" s="31" t="s">
-        <v>524</v>
+        <v>539</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E63" s="1" t="s">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>526</v>
+        <v>541</v>
       </c>
       <c r="K63" s="31" t="s">
-        <v>527</v>
+        <v>542</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E64" s="1" t="s">
-        <v>528</v>
+        <v>543</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="K64" s="31" t="s">
-        <v>530</v>
+        <v>545</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E65" s="1" t="s">
-        <v>531</v>
+        <v>546</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="K65" s="31" t="s">
-        <v>533</v>
+        <v>548</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E66" s="1" t="s">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="K66" s="31" t="s">
-        <v>536</v>
+        <v>551</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E67" s="1" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="K67" s="31" t="s">
-        <v>539</v>
+        <v>554</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E68" s="1" t="s">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="K68" s="31" t="s">
-        <v>542</v>
+        <v>557</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E69" s="1" t="s">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>544</v>
+        <v>559</v>
       </c>
       <c r="K69" s="31" t="s">
-        <v>545</v>
+        <v>560</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E70" s="1" t="s">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="K70" s="31" t="s">
-        <v>548</v>
+        <v>563</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E71" s="1" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="K71" s="31" t="s">
-        <v>551</v>
+        <v>566</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E72" s="1" t="s">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="K72" s="31" t="s">
-        <v>554</v>
+        <v>569</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E73" s="1" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="K73" s="31" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E74" s="1" t="s">
-        <v>558</v>
+        <v>573</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="K74" s="31" t="s">
-        <v>560</v>
+        <v>575</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E75" s="1" t="s">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="K75" s="31" t="s">
-        <v>563</v>
+        <v>578</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E76" s="1" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="K76" s="31" t="s">
-        <v>566</v>
+        <v>581</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E77" s="1" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="K77" s="31" t="s">
-        <v>569</v>
+        <v>584</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E78" s="1" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="K78" s="31" t="s">
-        <v>572</v>
+        <v>587</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E79" s="1" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="K79" s="31" t="s">
-        <v>575</v>
+        <v>590</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E80" s="1" t="s">
-        <v>576</v>
+        <v>591</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="K80" s="31" t="s">
-        <v>578</v>
+        <v>593</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E81" s="1" t="s">
-        <v>579</v>
+        <v>594</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="K81" s="31" t="s">
-        <v>581</v>
+        <v>596</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E82" s="1" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>583</v>
+        <v>598</v>
       </c>
       <c r="K82" s="31" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E83" s="1" t="s">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="K83" s="31" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E84" s="1" t="s">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="K84" s="31" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E85" s="1" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="K85" s="31" t="s">
-        <v>593</v>
+        <v>608</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E86" s="1" t="s">
-        <v>594</v>
+        <v>609</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>595</v>
+        <v>610</v>
       </c>
       <c r="K86" s="31" t="s">
-        <v>596</v>
+        <v>611</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E87" s="1" t="s">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>598</v>
+        <v>613</v>
       </c>
       <c r="K87" s="31" t="s">
-        <v>599</v>
+        <v>614</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E88" s="1" t="s">
-        <v>600</v>
+        <v>615</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>601</v>
+        <v>616</v>
       </c>
       <c r="K88" s="31" t="s">
-        <v>602</v>
+        <v>617</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E89" s="1" t="s">
-        <v>603</v>
+        <v>618</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
       <c r="K89" s="31" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E90" s="1" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
       <c r="K90" s="31" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E91" s="1" t="s">
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>610</v>
+        <v>625</v>
       </c>
       <c r="K91" s="31" t="s">
-        <v>611</v>
+        <v>626</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E92" s="1" t="s">
-        <v>612</v>
+        <v>627</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>613</v>
+        <v>628</v>
       </c>
       <c r="K92" s="31" t="s">
-        <v>614</v>
+        <v>629</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E93" s="1" t="s">
-        <v>615</v>
+        <v>630</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>616</v>
+        <v>631</v>
       </c>
       <c r="K93" s="31" t="s">
-        <v>617</v>
+        <v>632</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E94" s="1" t="s">
-        <v>618</v>
+        <v>633</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>619</v>
+        <v>634</v>
       </c>
       <c r="K94" s="31" t="s">
-        <v>620</v>
+        <v>635</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E95" s="1" t="s">
-        <v>621</v>
+        <v>636</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>622</v>
+        <v>637</v>
       </c>
       <c r="K95" s="31" t="s">
-        <v>623</v>
+        <v>638</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E96" s="1" t="s">
-        <v>624</v>
+        <v>639</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="K96" s="31" t="s">
-        <v>626</v>
+        <v>641</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E97" s="1" t="s">
-        <v>627</v>
+        <v>642</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>628</v>
+        <v>643</v>
       </c>
       <c r="K97" s="31" t="s">
-        <v>629</v>
+        <v>644</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E98" s="1" t="s">
-        <v>630</v>
+        <v>645</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>631</v>
+        <v>646</v>
       </c>
       <c r="K98" s="31" t="s">
-        <v>632</v>
+        <v>647</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E99" s="1" t="s">
-        <v>633</v>
+        <v>648</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>634</v>
+        <v>649</v>
       </c>
       <c r="K99" s="31" t="s">
-        <v>635</v>
+        <v>650</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E100" s="1" t="s">
-        <v>636</v>
+        <v>651</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>637</v>
+        <v>652</v>
       </c>
       <c r="K100" s="31" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E101" s="1" t="s">
-        <v>639</v>
+        <v>654</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="K101" s="31" t="s">
-        <v>641</v>
+        <v>656</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E102" s="1" t="s">
-        <v>642</v>
+        <v>657</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>643</v>
+        <v>658</v>
       </c>
       <c r="K102" s="31" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E103" s="1" t="s">
-        <v>645</v>
+        <v>660</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>646</v>
+        <v>661</v>
       </c>
       <c r="K103" s="31" t="s">
-        <v>647</v>
+        <v>662</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E104" s="1" t="s">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>649</v>
+        <v>664</v>
       </c>
       <c r="K104" s="31" t="s">
-        <v>650</v>
+        <v>665</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E105" s="1" t="s">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="K105" s="31" t="s">
-        <v>653</v>
+        <v>668</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E106" s="1" t="s">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="K106" s="31" t="s">
-        <v>655</v>
+        <v>670</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E107" s="1" t="s">
-        <v>656</v>
+        <v>671</v>
       </c>
       <c r="K107" s="31" t="s">
-        <v>657</v>
+        <v>672</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E108" s="1" t="s">
-        <v>658</v>
+        <v>673</v>
       </c>
       <c r="K108" s="31" t="s">
-        <v>659</v>
+        <v>674</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E109" s="1" t="s">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="K109" s="31" t="s">
-        <v>661</v>
+        <v>676</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E110" s="1" t="s">
-        <v>662</v>
+        <v>677</v>
       </c>
       <c r="K110" s="31" t="s">
-        <v>663</v>
+        <v>678</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E111" s="1" t="s">
-        <v>664</v>
+        <v>679</v>
       </c>
       <c r="K111" s="31" t="s">
-        <v>665</v>
+        <v>680</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E112" s="1" t="s">
-        <v>666</v>
+        <v>681</v>
       </c>
       <c r="K112" s="31" t="s">
-        <v>667</v>
+        <v>682</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E113" s="1" t="s">
-        <v>668</v>
+        <v>683</v>
       </c>
       <c r="K113" s="31" t="s">
-        <v>669</v>
+        <v>684</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E114" s="1" t="s">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="K114" s="31" t="s">
-        <v>671</v>
+        <v>686</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E115" s="1" t="s">
-        <v>672</v>
+        <v>687</v>
       </c>
       <c r="K115" s="31" t="s">
-        <v>673</v>
+        <v>688</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E116" s="1" t="s">
-        <v>674</v>
+        <v>689</v>
       </c>
       <c r="K116" s="31" t="s">
-        <v>675</v>
+        <v>690</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E117" s="1" t="s">
-        <v>676</v>
+        <v>691</v>
       </c>
       <c r="K117" s="31" t="s">
-        <v>677</v>
+        <v>692</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E118" s="1" t="s">
-        <v>678</v>
+        <v>693</v>
       </c>
       <c r="K118" s="31" t="s">
-        <v>679</v>
+        <v>694</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E119" s="1" t="s">
-        <v>680</v>
+        <v>695</v>
       </c>
       <c r="K119" s="31" t="s">
-        <v>681</v>
+        <v>696</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E120" s="1" t="s">
-        <v>682</v>
+        <v>697</v>
       </c>
       <c r="K120" s="31" t="s">
-        <v>683</v>
+        <v>698</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E121" s="1" t="s">
-        <v>684</v>
+        <v>699</v>
       </c>
       <c r="K121" s="31" t="s">
-        <v>685</v>
+        <v>700</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E122" s="1" t="s">
-        <v>686</v>
+        <v>701</v>
       </c>
       <c r="K122" s="31" t="s">
-        <v>687</v>
+        <v>702</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E123" s="1" t="s">
-        <v>688</v>
+        <v>703</v>
       </c>
       <c r="K123" s="31" t="s">
-        <v>689</v>
+        <v>704</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E124" s="1" t="s">
-        <v>690</v>
+        <v>705</v>
       </c>
       <c r="K124" s="31" t="s">
-        <v>691</v>
+        <v>706</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E125" s="1" t="s">
-        <v>692</v>
+        <v>707</v>
       </c>
       <c r="K125" s="31" t="s">
-        <v>693</v>
+        <v>708</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E126" s="1" t="s">
-        <v>694</v>
+        <v>709</v>
       </c>
       <c r="K126" s="31" t="s">
-        <v>695</v>
+        <v>710</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E127" s="1" t="s">
-        <v>696</v>
+        <v>711</v>
       </c>
       <c r="K127" s="31" t="s">
-        <v>697</v>
+        <v>712</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E128" s="1" t="s">
-        <v>698</v>
+        <v>713</v>
       </c>
       <c r="K128" s="31" t="s">
-        <v>699</v>
+        <v>714</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E129" s="1" t="s">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="K129" s="31" t="s">
-        <v>701</v>
+        <v>716</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E130" s="1" t="s">
-        <v>702</v>
+        <v>717</v>
       </c>
       <c r="K130" s="31" t="s">
-        <v>703</v>
+        <v>718</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E131" s="1" t="s">
-        <v>704</v>
+        <v>719</v>
       </c>
       <c r="K131" s="31" t="s">
-        <v>705</v>
+        <v>720</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E132" s="1" t="s">
-        <v>706</v>
+        <v>721</v>
       </c>
       <c r="K132" s="31" t="s">
-        <v>707</v>
+        <v>722</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E133" s="1" t="s">
-        <v>708</v>
+        <v>723</v>
       </c>
       <c r="K133" s="31" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E134" s="1" t="s">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="K134" s="31" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E135" s="1" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="K135" s="31" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E136" s="1" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="K136" s="31" t="s">
-        <v>715</v>
+        <v>730</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E137" s="1" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="K137" s="31" t="s">
-        <v>717</v>
+        <v>732</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E138" s="1" t="s">
-        <v>718</v>
+        <v>733</v>
       </c>
       <c r="K138" s="31" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E139" s="1" t="s">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="K139" s="31" t="s">
-        <v>721</v>
+        <v>736</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E140" s="1" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="K140" s="31" t="s">
-        <v>723</v>
+        <v>738</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E141" s="1" t="s">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="K141" s="31" t="s">
-        <v>725</v>
+        <v>740</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E142" s="1" t="s">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="K142" s="31" t="s">
-        <v>727</v>
+        <v>742</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E143" s="1" t="s">
-        <v>728</v>
+        <v>743</v>
       </c>
       <c r="K143" s="31" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E144" s="1" t="s">
-        <v>730</v>
+        <v>745</v>
       </c>
       <c r="K144" s="31" t="s">
-        <v>731</v>
+        <v>746</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E145" s="1" t="s">
-        <v>732</v>
+        <v>747</v>
       </c>
       <c r="K145" s="31" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E146" s="1" t="s">
-        <v>734</v>
+        <v>749</v>
       </c>
       <c r="K146" s="31" t="s">
-        <v>735</v>
+        <v>750</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E147" s="1" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="K147" s="31" t="s">
-        <v>737</v>
+        <v>752</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E148" s="1" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="K148" s="31" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E149" s="1" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="K149" s="31" t="s">
-        <v>741</v>
+        <v>756</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E150" s="1" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="K150" s="31" t="s">
-        <v>743</v>
+        <v>758</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E151" s="1" t="s">
-        <v>744</v>
+        <v>759</v>
       </c>
       <c r="K151" s="31" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E152" s="1" t="s">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="K152" s="31" t="s">
-        <v>747</v>
+        <v>762</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E153" s="1" t="s">
-        <v>748</v>
+        <v>763</v>
       </c>
       <c r="K153" s="31" t="s">
-        <v>749</v>
+        <v>764</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E154" s="1" t="s">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="K154" s="31" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E155" s="1" t="s">
-        <v>752</v>
+        <v>767</v>
       </c>
       <c r="K155" s="31" t="s">
-        <v>753</v>
+        <v>768</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E156" s="1" t="s">
-        <v>754</v>
+        <v>769</v>
       </c>
       <c r="K156" s="31" t="s">
-        <v>755</v>
+        <v>770</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E157" s="1" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="K157" s="31" t="s">
-        <v>757</v>
+        <v>772</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E158" s="1" t="s">
-        <v>758</v>
+        <v>773</v>
       </c>
       <c r="K158" s="31" t="s">
-        <v>759</v>
+        <v>774</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E159" s="1" t="s">
-        <v>760</v>
+        <v>775</v>
       </c>
       <c r="K159" s="31" t="s">
-        <v>761</v>
+        <v>776</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E160" s="1" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="K160" s="31" t="s">
-        <v>763</v>
+        <v>778</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E161" s="1" t="s">
-        <v>764</v>
+        <v>779</v>
       </c>
       <c r="K161" s="31" t="s">
-        <v>765</v>
+        <v>780</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E162" s="1" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="K162" s="31" t="s">
-        <v>767</v>
+        <v>782</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E163" s="1" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="K163" s="31" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E164" s="1" t="s">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="K164" s="31" t="s">
-        <v>771</v>
+        <v>786</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E165" s="1" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="K165" s="31" t="s">
-        <v>773</v>
+        <v>788</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E166" s="1" t="s">
-        <v>774</v>
+        <v>789</v>
       </c>
       <c r="K166" s="31" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E167" s="1" t="s">
-        <v>776</v>
+        <v>791</v>
       </c>
       <c r="K167" s="31" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E168" s="1" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="K168" s="31" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E169" s="1" t="s">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="K169" s="31" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E170" s="1" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="K170" s="31" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E171" s="1" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="K171" s="31" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E172" s="1" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="K172" s="31" t="s">
-        <v>787</v>
+        <v>802</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E173" s="1" t="s">
-        <v>788</v>
+        <v>803</v>
       </c>
       <c r="K173" s="31" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E174" s="1" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="K174" s="31" t="s">
-        <v>791</v>
+        <v>806</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E175" s="1" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="K175" s="31" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E176" s="1" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="K176" s="31" t="s">
-        <v>795</v>
+        <v>810</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E177" s="1" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="K177" s="31" t="s">
-        <v>797</v>
+        <v>812</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E178" s="1" t="s">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="K178" s="31" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E179" s="1" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="K179" s="31" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E180" s="1" t="s">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="K180" s="31" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E181" s="1" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="K181" s="31" t="s">
-        <v>805</v>
+        <v>820</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E182" s="1" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="K182" s="31" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E183" s="1" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="K183" s="31" t="s">
-        <v>809</v>
+        <v>824</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E184" s="1" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="K184" s="31" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E185" s="1" t="s">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="K185" s="31" t="s">
-        <v>813</v>
+        <v>828</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E186" s="1" t="s">
-        <v>814</v>
+        <v>829</v>
       </c>
       <c r="K186" s="31" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E187" s="1" t="s">
-        <v>816</v>
+        <v>831</v>
       </c>
       <c r="K187" s="31" t="s">
-        <v>817</v>
+        <v>832</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E188" s="1" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="K188" s="31" t="s">
-        <v>819</v>
+        <v>834</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E189" s="1" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="K189" s="31" t="s">
-        <v>821</v>
+        <v>836</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E190" s="1" t="s">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="K190" s="31" t="s">
-        <v>823</v>
+        <v>838</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E191" s="1" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="K191" s="31" t="s">
-        <v>825</v>
+        <v>840</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E192" s="1" t="s">
-        <v>826</v>
+        <v>841</v>
       </c>
       <c r="K192" s="31" t="s">
-        <v>827</v>
+        <v>842</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E193" s="1" t="s">
-        <v>828</v>
+        <v>843</v>
       </c>
       <c r="K193" s="31" t="s">
-        <v>829</v>
+        <v>844</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E194" s="1" t="s">
-        <v>830</v>
+        <v>845</v>
       </c>
       <c r="K194" s="31" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E195" s="1" t="s">
-        <v>832</v>
+        <v>847</v>
       </c>
       <c r="K195" s="31" t="s">
-        <v>833</v>
+        <v>848</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E196" s="1" t="s">
-        <v>834</v>
+        <v>849</v>
       </c>
       <c r="K196" s="31" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E197" s="1" t="s">
-        <v>835</v>
+        <v>850</v>
       </c>
       <c r="K197" s="31" t="s">
-        <v>836</v>
+        <v>851</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E198" s="1" t="s">
-        <v>837</v>
+        <v>852</v>
       </c>
       <c r="K198" s="31" t="s">
-        <v>838</v>
+        <v>853</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E199" s="1" t="s">
-        <v>839</v>
+        <v>854</v>
       </c>
       <c r="K199" s="31" t="s">
-        <v>840</v>
+        <v>855</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K200" s="31" t="s">
-        <v>841</v>
+        <v>856</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K201" s="31" t="s">
-        <v>842</v>
+        <v>857</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K202" s="31" t="s">
-        <v>843</v>
+        <v>858</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K203" s="31" t="s">
-        <v>844</v>
+        <v>859</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K204" s="31" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K205" s="31" t="s">
-        <v>846</v>
+        <v>861</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K206" s="31" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K207" s="31" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K208" s="31" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K209" s="31" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K210" s="31" t="s">
-        <v>841</v>
+        <v>856</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K211" s="31" t="s">
-        <v>851</v>
+        <v>866</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K212" s="31" t="s">
-        <v>852</v>
+        <v>867</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K213" s="31" t="s">
-        <v>853</v>
+        <v>868</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K214" s="31" t="s">
-        <v>854</v>
+        <v>869</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K215" s="31" t="s">
-        <v>855</v>
+        <v>870</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K216" s="31" t="s">
-        <v>856</v>
+        <v>871</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K217" s="31" t="s">
-        <v>857</v>
+        <v>872</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K218" s="31" t="s">
-        <v>858</v>
+        <v>873</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K219" s="31" t="s">
-        <v>859</v>
+        <v>874</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K220" s="31" t="s">
-        <v>860</v>
+        <v>875</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K221" s="31" t="s">
-        <v>861</v>
+        <v>876</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K222" s="31" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K223" s="31" t="s">
-        <v>863</v>
+        <v>878</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K224" s="31" t="s">
-        <v>864</v>
+        <v>879</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K225" s="31" t="s">
-        <v>865</v>
+        <v>880</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K226" s="31" t="s">
-        <v>866</v>
+        <v>881</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K227" s="31" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K228" s="31" t="s">
-        <v>868</v>
+        <v>883</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K229" s="31" t="s">
-        <v>869</v>
+        <v>884</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K230" s="31" t="s">
-        <v>870</v>
+        <v>885</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K231" s="31" t="s">
-        <v>871</v>
+        <v>886</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K232" s="31" t="s">
-        <v>872</v>
+        <v>887</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K233" s="31" t="s">
-        <v>873</v>
+        <v>888</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K234" s="31" t="s">
-        <v>874</v>
+        <v>889</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K235" s="31" t="s">
-        <v>875</v>
+        <v>890</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K236" s="31" t="s">
-        <v>876</v>
+        <v>891</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K237" s="31" t="s">
-        <v>877</v>
+        <v>892</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K238" s="31" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K239" s="31" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K240" s="31" t="s">
-        <v>880</v>
+        <v>895</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K241" s="31" t="s">
-        <v>881</v>
+        <v>896</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K242" s="31" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K243" s="31" t="s">
-        <v>883</v>
+        <v>898</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K244" s="31" t="s">
-        <v>884</v>
+        <v>899</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K245" s="31" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K246" s="31" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K247" s="31" t="s">
-        <v>887</v>
+        <v>902</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K248" s="31" t="s">
-        <v>888</v>
+        <v>903</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K249" s="31" t="s">
-        <v>889</v>
+        <v>904</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K250" s="31" t="s">
-        <v>890</v>
+        <v>905</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K251" s="31" t="s">
-        <v>891</v>
+        <v>906</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K252" s="31" t="s">
-        <v>892</v>
+        <v>907</v>
       </c>
     </row>
   </sheetData>
